--- a/powerball_draws_full.xlsx
+++ b/powerball_draws_full.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1957"/>
+  <dimension ref="A1:L1958"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81794,6 +81794,48 @@
         </is>
       </c>
     </row>
+    <row r="1958">
+      <c r="A1958" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B1958" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C1958" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1958" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1958" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="F1958" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1958" t="n">
+        <v>24</v>
+      </c>
+      <c r="H1958" t="n">
+        <v>34</v>
+      </c>
+      <c r="I1958" t="n">
+        <v>43</v>
+      </c>
+      <c r="J1958" t="n">
+        <v>49</v>
+      </c>
+      <c r="K1958" t="n">
+        <v>20</v>
+      </c>
+      <c r="L1958" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/powerball_draws_full.xlsx
+++ b/powerball_draws_full.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1958"/>
+  <dimension ref="A1:L1959"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81836,6 +81836,48 @@
         </is>
       </c>
     </row>
+    <row r="1959">
+      <c r="A1959" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B1959" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C1959" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1959" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1959" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="F1959" t="n">
+        <v>12</v>
+      </c>
+      <c r="G1959" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1959" t="n">
+        <v>38</v>
+      </c>
+      <c r="I1959" t="n">
+        <v>60</v>
+      </c>
+      <c r="J1959" t="n">
+        <v>66</v>
+      </c>
+      <c r="K1959" t="n">
+        <v>14</v>
+      </c>
+      <c r="L1959" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
